--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kind" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preferred sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching rules" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins each field" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matching rules" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -574,6 +575,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MDM field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Filled by, first wins</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>fiscal_year_end</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>gleif_entity_creation_date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>gleif_entity_status</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>gleif_initial_registration</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>gleif_last_update</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>gleif_legal_form</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>gleif_managing_lou</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>gleif_next_renewal</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_authority</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_authority_entity_id</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_status</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>gleif_validation_source</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>sic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>sic_description</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>state_of_incorporation</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -658,7 +1119,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: sic; values: 6189)</t>
+          <t>sic is one of: 6189</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -700,7 +1161,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: sic; values: 6221)</t>
+          <t>sic is one of: 6221</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -742,7 +1203,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: sic; values: 8888)</t>
+          <t>sic is one of: 8888</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -784,7 +1245,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>fields_all_empty@1(fields: ticker); token_match@2(field: category; normalizer: conformed; token_list: emerging_growth; min_count: 1)</t>
+          <t>ticker is empty; and category holds at least 1 word(s) of the list emerging_growth</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -826,7 +1287,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); token_match@2(field: entity_name; normalizer: conformed; token_list: fund_name; min_count: 1)</t>
+          <t>entity_type is one of: operating; and entity_name holds at least 1 word(s) of the list fund_name</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -868,7 +1329,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); field_in_set@1(field: sic; values: 6199, 6211, 6282, 6799, 6798); field_in_set@1(field: category; values: &lt;br&gt;Emerging growth company)</t>
+          <t>entity_type is one of: operating; and sic is one of: 6199, 6211, 6282, 6799, 6798; and category is one of: &lt;br&gt;Emerging growth company</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -910,7 +1371,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); field_in_set@1(field: sic; values: 6798); fields_all_empty@1(fields: ticker)</t>
+          <t>entity_type is one of: operating; and sic is one of: 6798; and ticker is empty</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -948,7 +1409,7 @@
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); fields_all_empty@1(fields: industry_code)</t>
+          <t>entity_type is one of: operating; and industry_code is empty</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -990,7 +1451,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); values_overlap@1(field: forms; values: fund_report; min_count: 1)</t>
+          <t>entity_type is one of: operating; and forms holds at least 1 of the list fund_report</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1032,7 +1493,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating); values_overlap@1(field: forms; values: form_10; min_count: 1); values_overlap@1(field: forms; values: private_offering; min_count: 1); values_overlap@1(field: forms; values: bdc_election; max_count: 0)</t>
+          <t>entity_type is one of: operating; and forms holds at least 1 of the list form_10; and forms holds at least 1 of the list private_offering; and forms holds at least  of the list bdc_election</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1070,7 +1531,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: operating)</t>
+          <t>entity_type is one of: operating</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1112,7 +1573,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: other); token_match@2(field: entity_name; normalizer: conformed; token_list: person_suffix; min_count: 1)</t>
+          <t>entity_type is one of: other; and entity_name holds at least 1 word(s) of the list person_suffix</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1150,7 +1611,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>field_in_set@1(field: entity_type; values: other); evidence_present@1(document: sic); evidence_present@1(document: category); token_match@2(field: entity_name; normalizer: conformed; token_list: company_legal_form; min_count: 1)</t>
+          <t>entity_type is one of: other; and The record has sic; and The record has category; and entity_name holds at least 1 word(s) of the list company_legal_form</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1188,7 +1649,7 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>otherwise</t>
+          <t>Otherwise</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1202,7 +1663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1291,7 +1752,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>name_census_match@1(sec_normalizer: normalize_text@sec-legal-form-kept-v1; gleif_normalizer: normalize_text@legal-form-kept-v1); gleif_entity_eligible@1(categories: GENERAL; entity_statuses: ACTIVE; refused_registration_statuses: ANNULLED, DUPLICATE); holds_no_other_lei@1(); jurisdiction_agrees@1(sec_field: state_of_incorporation; sec_codes: edgar-iso-v1; gleif_field: jurisdiction)</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1333,7 +1794,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>name_census_match@1(sec_normalizer: normalize_text@sec-legal-form-kept-v1; gleif_normalizer: normalize_text@legal-form-kept-v1); gleif_entity_eligible@1(categories: GENERAL; entity_statuses: ACTIVE; refused_registration_statuses: ANNULLED, DUPLICATE); holds_no_other_lei@1(); jurisdictions_do_not_conflict@1(sec_field: state_of_incorporation; sec_codes: edgar-iso-v1; gleif_field: jurisdiction; sec_business_country: matching.business_country); postal_agrees@1(sec_code: matching.business_postal_code; sec_country: matching.business_country; gleif_code: matching.headquarters_postal_code; gleif_country: matching.headquarters_country)</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1352,7 +1813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1405,7 +1866,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1423,7 +1884,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -575,13 +575,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,6 +603,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Rules path</t>
         </is>
       </c>
@@ -624,6 +630,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -646,6 +657,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -668,6 +684,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -690,6 +711,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -712,6 +738,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -734,6 +765,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -756,6 +792,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -778,6 +819,11 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -800,6 +846,11 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -822,6 +873,11 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -844,6 +900,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -866,6 +927,11 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -888,6 +954,11 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -910,6 +981,11 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -932,6 +1008,11 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -954,6 +1035,11 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -976,6 +1062,11 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -998,6 +1089,11 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -1019,6 +1115,11 @@
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1770,7 +1770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1906,300 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p2</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p3</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p4</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[6]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p5</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p6</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[8]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>sec-gleif-cascade-p7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[9]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1770,17 +1770,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1833,32 +1833,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-jurisdiction</t>
+          <t>company-cik</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.1</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
+          <t>The record's cik is the one a Company holds; and Exactly one Company holds that cik, or none (a miss does what the rule says)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-postal</t>
+          <t>sec-gleif-name-jurisdiction</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.2</t>
+          <t>2026-09-25.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1895,7 +1891,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1917,12 +1913,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p1</t>
+          <t>sec-gleif-name-postal</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-09-25.2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1937,7 +1933,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1959,7 +1955,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p2</t>
+          <t>sec-gleif-cascade-p1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1979,7 +1975,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p3</t>
+          <t>sec-gleif-cascade-p2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2021,7 +2017,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2043,7 +2039,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p4</t>
+          <t>sec-gleif-cascade-p3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2063,7 +2059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2085,7 +2081,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p5</t>
+          <t>sec-gleif-cascade-p4</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2105,7 +2101,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p6</t>
+          <t>sec-gleif-cascade-p5</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2147,7 +2143,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2169,37 +2165,79 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>sec-gleif-cascade-p6</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[9]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>sec-gleif-cascade-p7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-09-28.1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[9]</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[10]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1849,7 +1849,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The record's cik is the one a Company holds; and Exactly one Company holds that cik, or none (a miss does what the rule says)</t>
+          <t>The record's CIK is the one a Company holds; and Exactly one Company holds that CIK, or none</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1770,17 +1770,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1833,32 +1833,28 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-jurisdiction</t>
+          <t>company-cik</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.1</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
+          <t>The record's CIK is the one a Company holds; and Exactly one Company holds that CIK, or none</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1875,12 +1871,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-postal</t>
+          <t>sec-gleif-name-jurisdiction</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.2</t>
+          <t>2026-09-25.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1895,7 +1891,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1917,12 +1913,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p1</t>
+          <t>sec-gleif-name-postal</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-09-25.2</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1937,7 +1933,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1959,7 +1955,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p2</t>
+          <t>sec-gleif-cascade-p1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1979,7 +1975,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p3</t>
+          <t>sec-gleif-cascade-p2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2021,7 +2017,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2043,7 +2039,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p4</t>
+          <t>sec-gleif-cascade-p3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2063,7 +2059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2085,7 +2081,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p5</t>
+          <t>sec-gleif-cascade-p4</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2105,7 +2101,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p6</t>
+          <t>sec-gleif-cascade-p5</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2147,7 +2143,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2169,37 +2165,79 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>sec-gleif-cascade-p6</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28.1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>wait</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[9]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>sec-gleif-cascade-p7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>2026-09-28.1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[9]</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[10]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,23 @@
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[2]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -578,6 +578,40 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custody.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[4]</t>
         </is>
       </c>
     </row>
@@ -596,7 +630,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
@@ -637,7 +671,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1042,7 +1076,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1787,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2289,120 @@
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-crd</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-custodian-lei</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custody.v1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-custodian-bd</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custody.v1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[13]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custody.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -578,6 +578,40 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[4]</t>
         </is>
       </c>
     </row>
@@ -596,7 +630,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
@@ -637,7 +671,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1042,7 +1076,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1787,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2289,120 @@
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-crd</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[11]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-custodian-lei</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[12]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-custodian-bd</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[13]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -612,6 +612,23 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources[4]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>sec.nport.registrant.v1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources[5]</t>
         </is>
       </c>
     </row>
@@ -671,7 +688,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1076,7 +1093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1821,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1922,32 +1939,28 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-jurisdiction</t>
+          <t>nport-registrant-cik</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.1</t>
+          <t>2026-10-15.1</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>sec.nport.registrant.v1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
+          <t>The record's CIK is the one a Company holds; and Exactly one Company holds that CIK, or none</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1964,12 +1977,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-name-postal</t>
+          <t>sec-gleif-name-jurisdiction</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-25.2</t>
+          <t>2026-09-25.1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1984,7 +1997,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation names the same place as GLEIF's jurisdiction</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2006,12 +2019,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p1</t>
+          <t>sec-gleif-name-postal</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-09-25.2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2026,7 +2039,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The names are equal, legal form kept, and exactly one SEC filer and one GLEIF entity carry that name; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI; and SEC's state_of_incorporation and GLEIF's jurisdiction do not name different places; and SEC's business postcode equals GLEIF's headquarters postcode, in the same country</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2048,7 +2061,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p2</t>
+          <t>sec-gleif-cascade-p1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2068,7 +2081,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,7 +2103,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p3</t>
+          <t>sec-gleif-cascade-p2</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2110,7 +2123,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2132,7 +2145,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p4</t>
+          <t>sec-gleif-cascade-p3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2152,7 +2165,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2174,7 +2187,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p5</t>
+          <t>sec-gleif-cascade-p4</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2194,7 +2207,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2216,7 +2229,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p6</t>
+          <t>sec-gleif-cascade-p5</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2236,7 +2249,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2258,7 +2271,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p7</t>
+          <t>sec-gleif-cascade-p6</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2278,7 +2291,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2300,28 +2313,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-crd</t>
+          <t>sec-gleif-cascade-p7</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09.1</t>
+          <t>2026-09-28.1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.filings.v1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2338,7 +2355,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-custodian-lei</t>
+          <t>iapd-adv-crd</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2348,13 +2365,13 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custodians.v1</t>
+          <t>iapd.adv.filings.v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2376,7 +2393,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-custodian-bd</t>
+          <t>iapd-adv-custodian-lei</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2392,17 +2409,55 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[13]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>iapd-adv-custodian-bd</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09.1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>mint</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[13]</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[14]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ticker is empty; and category holds at least 1 word(s) of the list emerging_growth</t>
+          <t>ticker is empty; and category holds at least 1 of the words of the list emerging_growth</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: operating; and entity_name holds at least 1 word(s) of the list fund_name</t>
+          <t>entity_type is one of: operating; and entity_name holds at least 1 of the words of the list fund_name</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: operating; and forms holds at least 1 of the list form_10; and forms holds at least 1 of the list private_offering; and forms holds at least  of the list bdc_election</t>
+          <t>entity_type is one of: operating; and forms holds at least 1 of the list form_10; and forms holds at least 1 of the list private_offering; and forms holds none of the list bdc_election</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: other; and entity_name holds at least 1 word(s) of the list person_suffix</t>
+          <t>entity_type is one of: other; and entity_name holds at least 1 of the words of the list person_suffix</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: other; and The record has sic; and The record has category; and entity_name holds at least 1 word(s) of the list company_legal_form</t>
+          <t>entity_type is one of: other; and The record has sic; and The record has category; and entity_name holds at least 1 of the words of the list company_legal_form</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ticker is empty; and category holds at least 1 word(s) of the list emerging_growth</t>
+          <t>ticker is empty; and category holds at least 1 of the words of the list emerging_growth</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: operating; and entity_name holds at least 1 word(s) of the list fund_name</t>
+          <t>entity_type is one of: operating; and entity_name holds at least 1 of the words of the list fund_name</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: operating; and forms holds at least 1 of the list form_10; and forms holds at least 1 of the list private_offering; and forms holds at least  of the list bdc_election</t>
+          <t>entity_type is one of: operating; and forms holds at least 1 of the list form_10; and forms holds at least 1 of the list private_offering; and forms holds none of the list bdc_election</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: other; and entity_name holds at least 1 word(s) of the list person_suffix</t>
+          <t>entity_type is one of: other; and entity_name holds at least 1 of the words of the list person_suffix</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>entity_type is one of: other; and The record has sic; and The record has category; and entity_name holds at least 1 word(s) of the list company_legal_form</t>
+          <t>entity_type is one of: other; and The record has sic; and The record has category; and entity_name holds at least 1 of the words of the list company_legal_form</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: ; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1838,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2458,6 +2458,44 @@
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[14]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>gleif-issuer-lei</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16.1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>The record has provenance.matching.nport_issuer; and The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>mint</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml rules[15]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16.1</t>
+          <t>2026-10-16.2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1838,7 +1838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p2</t>
+          <t>sec-gleif-cascade-p4</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P2: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p3</t>
+          <t>sec-gleif-cascade-p5</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P3: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p4</t>
+          <t>sec-gleif-cascade-p6</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p5</t>
+          <t>sec-gleif-cascade-p7</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2271,32 +2271,28 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p6</t>
+          <t>iapd-adv-crd</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-10-09.1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2313,32 +2309,28 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p7</t>
+          <t>iapd-adv-custodian-lei</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-10-09.1</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2355,7 +2347,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-crd</t>
+          <t>iapd-adv-custodian-bd</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2365,13 +2357,13 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.filings.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
+          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2393,109 +2385,33 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-custodian-lei</t>
+          <t>gleif-issuer-lei</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09.1</t>
+          <t>2026-10-16.2</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custodians.v1</t>
+          <t>gleif.level1.v1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+          <t>The record has provenance.matching.nport_issuer; and The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[13]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>iapd-adv-custodian-bd</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09.1</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>iapd.adv.custodians.v1</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>mint</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[14]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>gleif-issuer-lei</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16.2</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>The record has provenance.matching.nport_issuer; and The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>wait</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[15]</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -845,7 +845,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gleif_last_update</t>
+          <t>gleif_legal_form</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>gleif_legal_form</t>
+          <t>gleif_managing_lou</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>gleif_managing_lou</t>
+          <t>gleif_registration_authority</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>gleif_next_renewal</t>
+          <t>gleif_registration_authority_entity_id</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority</t>
+          <t>gleif_registration_status</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority_entity_id</t>
+          <t>gleif_validation_source</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1007,7 +1007,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_status</t>
+          <t>jurisdiction</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1034,17 +1034,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>gleif_validation_source</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>jurisdiction</t>
+          <t>sic</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>state_of_incorporation</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
+          <t>sec.submissions.company.v1</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1107,87 +1107,6 @@
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>sic</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>sic_description</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>state_of_incorporation</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>company-2026-09-25.13</t>
+          <t>company-2026-10-25.one-value-per-identifier</t>
         </is>
       </c>
     </row>

--- a/rules/merge/kinds/company.xlsx
+++ b/rules/merge/kinds/company.xlsx
@@ -1757,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p1</t>
+          <t>sec-gleif-cascade-p5</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-10-30.1</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pass P1: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, street, city, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city or postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p4</t>
+          <t>sec-gleif-cascade-p6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Pass P4: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, postcode. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p5</t>
+          <t>sec-gleif-cascade-p7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Pass P5: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country, city. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2106,32 +2106,28 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p6</t>
+          <t>iapd-adv-crd</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-10-09.1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>iapd.adv.filings.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Pass P6: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the country. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2148,32 +2144,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>sec-gleif-cascade-p7</t>
+          <t>iapd-adv-custodian-lei</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28.1</t>
+          <t>2026-10-09.1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
+          <t>iapd.adv.custodians.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Pass P7: the names are equal, legal form kept (GLEIF's other names count), and, of what earlier passes left, exactly one SEC company and one GLEIF entity agree on the name alone. An address more than 25 entities share counts by its country only. Refused flags: none; and The GLEIF entity is GENERAL, ACTIVE, and not ANNULLED, DUPLICATE; and The SEC company is not already linked to another LEI</t>
+          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>wait</t>
+          <t>mint</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2190,7 +2182,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-crd</t>
+          <t>iapd-adv-custodian-bd</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2200,13 +2192,13 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.filings.v1</t>
+          <t>iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>The record's CRD is the one a Company holds; and Exactly one Company holds that CRD, or none</t>
+          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2228,109 +2220,33 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>iapd-adv-custodian-lei</t>
+          <t>gleif-issuer-lei</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09.1</t>
+          <t>2026-10-16.2</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>iapd.adv.custodians.v1</t>
+          <t>gleif.level1.v1</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+          <t>The record has provenance.matching.nport_issuer; and The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>mint</t>
+          <t>wait</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml rules[11]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>iapd-adv-custodian-bd</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-09.1</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>iapd.adv.custodians.v1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>The record's BD_NUMBER is the one a Company holds; and Exactly one Company holds that BD_NUMBER, or none</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>mint</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[12]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>gleif-issuer-lei</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16.2</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The record has provenance.matching.nport_issuer; and The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>wait</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml rules[13]</t>
         </is>
       </c>
     </row>
